--- a/TeplosilaWeb/Content/properties/htrv3s.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv3s.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Документы\ТЗ программа подбора TRV, RDT\ТЗ клапаны TRV\31.01.2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\properties\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533DA400-B3EF-41A7-9F45-09E0BFDB22BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{604B6695-66D5-4FC8-BD78-F97F1923A89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5025" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="48">
   <si>
     <t>Условный диаметр DN, мм</t>
   </si>
@@ -91,13 +94,7 @@
     <t>TSL-3000-60-1-230-IP67</t>
   </si>
   <si>
-    <t>TSL-1600-25-1T-230-IP67</t>
-  </si>
-  <si>
     <t>TSL-1600-25-1TR-230-IP67</t>
-  </si>
-  <si>
-    <t>TSL-2200-40-1T-230-IP67</t>
   </si>
   <si>
     <t>TSL-2200-40-1TR-230-IP67</t>
@@ -169,13 +166,25 @@
   </si>
   <si>
     <t>TRV-3 смесительный</t>
+  </si>
+  <si>
+    <t>TSL-1600-25-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-2200-40-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-60-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-40-1RS-230-IP67</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,19 +246,28 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -325,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -353,8 +371,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -368,14 +395,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -657,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -672,50 +699,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
+      <c r="A1" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="3">
         <v>53</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="20">
         <v>54</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>55</v>
@@ -746,88 +773,88 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="11" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11" t="s">
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="W3" s="11" t="s">
+      <c r="T3" s="21"/>
+      <c r="U3" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="V3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="11" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="17" t="s">
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="U4" s="17"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
+      <c r="T4" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" s="21"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
     </row>
     <row r="5" spans="1:23" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
       <c r="C5" s="5">
         <v>15</v>
       </c>
@@ -864,15 +891,15 @@
       <c r="N5" s="5">
         <v>200</v>
       </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="19"/>
     </row>
     <row r="6" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
@@ -997,7 +1024,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="6">
         <v>16</v>
@@ -1052,61 +1079,61 @@
       </c>
     </row>
     <row r="9" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+      <c r="A9" s="11">
         <v>4</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="6">
-        <v>16</v>
-      </c>
-      <c r="D9" s="6">
-        <v>16</v>
-      </c>
-      <c r="E9" s="6">
-        <v>16</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="B9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="11">
+        <v>16</v>
+      </c>
+      <c r="D9" s="11">
+        <v>16</v>
+      </c>
+      <c r="E9" s="11">
+        <v>16</v>
+      </c>
+      <c r="F9" s="11">
         <v>14</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="11">
         <v>8</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="11">
         <v>5.8</v>
       </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q9" s="6">
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q9" s="11">
         <v>1600</v>
       </c>
-      <c r="R9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="T9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="V9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="W9" s="6">
+      <c r="R9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="W9" s="11">
         <v>10</v>
       </c>
     </row>
@@ -1115,7 +1142,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="6">
         <v>16</v>
@@ -1174,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="6">
         <v>16</v>
@@ -1233,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" s="6">
         <v>16</v>
@@ -1292,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" s="6">
         <v>16</v>
@@ -1351,7 +1378,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="6">
         <v>16</v>
@@ -1516,7 +1543,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1565,55 +1592,55 @@
       </c>
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="6">
+      <c r="A18" s="11">
         <v>13</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6">
+      <c r="B18" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11">
         <v>6</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="11">
         <v>4.2</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="11">
         <v>2.6</v>
       </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q18" s="6">
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q18" s="11">
         <v>2200</v>
       </c>
-      <c r="R18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="T18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="V18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="W18" s="6">
+      <c r="R18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="W18" s="11">
         <v>10</v>
       </c>
     </row>
@@ -1622,7 +1649,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -1675,7 +1702,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -1728,7 +1755,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -1781,7 +1808,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -1834,7 +1861,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -1934,53 +1961,53 @@
       </c>
     </row>
     <row r="25" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
+      <c r="A25" s="11">
         <v>20</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6">
+      <c r="B25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11">
         <v>2.5</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="11">
         <v>1.5</v>
       </c>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="P25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q25" s="6">
+      <c r="N25" s="11"/>
+      <c r="O25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q25" s="11">
         <v>3000</v>
       </c>
-      <c r="R25" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="S25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="T25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="V25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="W25" s="6">
+      <c r="R25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="W25" s="11">
         <v>12</v>
       </c>
     </row>
@@ -1989,7 +2016,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -2007,82 +2034,82 @@
         <v>1.5</v>
       </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q26" s="9">
+      <c r="O26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q26" s="6">
         <v>3000</v>
       </c>
-      <c r="R26" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="S26" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="T26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="U26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="W26" s="9">
+      <c r="R26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="T26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="V26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="W26" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="6">
+      <c r="A27" s="11">
         <v>22</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6">
+      <c r="B27" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="11">
         <v>2.5</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="11">
         <v>1.5</v>
       </c>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="P27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q27" s="6">
+      <c r="N27" s="11"/>
+      <c r="O27" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q27" s="14">
         <v>3000</v>
       </c>
-      <c r="R27" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="S27" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="T27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="U27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="V27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="W27" s="6">
+      <c r="R27" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="V27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="W27" s="11">
         <v>12</v>
       </c>
     </row>
@@ -2091,7 +2118,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -2102,45 +2129,47 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6">
-        <v>2</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>6000</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="S28" s="6" t="s">
+      <c r="L28" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="M28" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>3000</v>
+      </c>
+      <c r="R28" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="S28" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="U28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="V28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="W28" s="18">
+      <c r="T28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="U28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="V28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="W28" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -2151,44 +2180,141 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6">
+      <c r="L29" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="M29" s="6">
         <v>1.5</v>
       </c>
-      <c r="O29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q29" s="9">
+      <c r="N29" s="6"/>
+      <c r="O29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>3000</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="T29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="W29" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="6">
+        <v>25</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6">
+        <v>2</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>6000</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="T30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="V30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="W30" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>26</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q31" s="9">
         <v>5000</v>
       </c>
-      <c r="R29" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="S29" s="9" t="s">
+      <c r="R31" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="U29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="V29" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="W29" s="9">
+      <c r="T31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="U31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="V31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="W31" s="9">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="C4:N4"/>
     <mergeCell ref="A1:W1"/>
@@ -2203,6 +2329,9 @@
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
